--- a/exps/data/train.xlsx
+++ b/exps/data/train.xlsx
@@ -19525,7 +19525,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Hà Nội.</t>
+          <t>Hà Nội</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -48304,7 +48304,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>Hà Nội.</t>
+          <t>Hà Nội</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -53922,7 +53922,7 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>Hà Nội.</t>
+          <t>Hà Nội</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
